--- a/artfynd/S 2741-2022 artfynd.xlsx
+++ b/artfynd/S 2741-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,48 +1570,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6792797</v>
+        <v>136643875</v>
       </c>
       <c r="B10" t="n">
-        <v>106812</v>
+        <v>9417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>101246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Enerums stugby syd, Öl</t>
+          <t>Enerum träsgate 81, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619700</v>
+        <v>619921</v>
       </c>
       <c r="R10" t="n">
-        <v>6353357</v>
+        <v>6353596</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,12 +1644,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ekoxehane gick på gräsmattan med något</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,31 +1679,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6792797</t>
+          <t>https://artportalen.se/Sighting/136643875</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103079105</v>
+        <v>6792797</v>
       </c>
       <c r="B11" t="n">
-        <v>106813</v>
+        <v>106812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,28 +1724,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerums stugby syd, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619932</v>
+        <v>619700</v>
       </c>
       <c r="R11" t="n">
-        <v>6353374</v>
+        <v>6353357</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,19 +1759,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9941A4BE-DBC1-4595-919E-A05E3D0A48C1</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,35 +1775,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079105</t>
+          <t>https://artportalen.se/Sighting/6792797</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103079896</v>
+        <v>103079105</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1829,16 +1835,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619840</v>
+        <v>619932</v>
       </c>
       <c r="R12" t="n">
-        <v>6353392</v>
+        <v>6353374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1875,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>FAD09A84-F0E6-4C8C-BF58-B5A1D0556E15</t>
+          <t>9941A4BE-DBC1-4595-919E-A05E3D0A48C1</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1884,6 +1894,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1905,13 +1916,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079896</t>
+          <t>https://artportalen.se/Sighting/103079105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103079897</v>
+        <v>103079896</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -1950,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619800</v>
+        <v>619840</v>
       </c>
       <c r="R13" t="n">
-        <v>6353369</v>
+        <v>6353392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,17 +1991,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7F4B304E-7E1B-424B-B267-E43505E0BEA5</t>
+          <t>FAD09A84-F0E6-4C8C-BF58-B5A1D0556E15</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,13 +2031,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079897</t>
+          <t>https://artportalen.se/Sighting/103079896</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103079898</v>
+        <v>103079897</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2065,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619791</v>
+        <v>619800</v>
       </c>
       <c r="R14" t="n">
-        <v>6353395</v>
+        <v>6353369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2106,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7FEE4EE0-1B0B-48CA-BBDB-CA3567C9C971</t>
+          <t>7F4B304E-7E1B-424B-B267-E43505E0BEA5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2135,13 +2146,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079898</t>
+          <t>https://artportalen.se/Sighting/103079897</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103079899</v>
+        <v>103079898</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2180,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619757</v>
+        <v>619791</v>
       </c>
       <c r="R15" t="n">
-        <v>6353389</v>
+        <v>6353395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2221,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>C935943E-6B16-4DE0-848B-12C1A3E2A805</t>
+          <t>7FEE4EE0-1B0B-48CA-BBDB-CA3567C9C971</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2250,13 +2261,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079899</t>
+          <t>https://artportalen.se/Sighting/103079898</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103079900</v>
+        <v>103079899</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2295,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619775</v>
+        <v>619757</v>
       </c>
       <c r="R16" t="n">
-        <v>6353420</v>
+        <v>6353389</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2336,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6DF65344-1F4B-4A55-A402-524F572C5D86</t>
+          <t>C935943E-6B16-4DE0-848B-12C1A3E2A805</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2365,13 +2376,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079900</t>
+          <t>https://artportalen.se/Sighting/103079899</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103079901</v>
+        <v>103079900</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2410,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619805</v>
+        <v>619775</v>
       </c>
       <c r="R17" t="n">
-        <v>6353446</v>
+        <v>6353420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2451,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>12EA338A-A207-47A3-96EC-3D50A58263E0</t>
+          <t>6DF65344-1F4B-4A55-A402-524F572C5D86</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2480,13 +2491,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079901</t>
+          <t>https://artportalen.se/Sighting/103079900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103079903</v>
+        <v>103079901</v>
       </c>
       <c r="B18" t="n">
         <v>106813</v>
@@ -2525,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619833</v>
+        <v>619805</v>
       </c>
       <c r="R18" t="n">
-        <v>6353565</v>
+        <v>6353446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2566,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>F98CE84B-7E58-40D3-BA79-B2311CC272D4</t>
+          <t>12EA338A-A207-47A3-96EC-3D50A58263E0</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2595,13 +2606,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079903</t>
+          <t>https://artportalen.se/Sighting/103079901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103079904</v>
+        <v>103079903</v>
       </c>
       <c r="B19" t="n">
         <v>106813</v>
@@ -2640,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619908</v>
+        <v>619833</v>
       </c>
       <c r="R19" t="n">
-        <v>6353503</v>
+        <v>6353565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,7 +2681,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>89CD7B68-5B89-4E5C-96E1-DBEE32490567</t>
+          <t>F98CE84B-7E58-40D3-BA79-B2311CC272D4</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2710,13 +2721,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079904</t>
+          <t>https://artportalen.se/Sighting/103079903</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103079905</v>
+        <v>103079904</v>
       </c>
       <c r="B20" t="n">
         <v>106813</v>
@@ -2755,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619653</v>
+        <v>619908</v>
       </c>
       <c r="R20" t="n">
-        <v>6353426</v>
+        <v>6353503</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,17 +2796,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
+          <t>89CD7B68-5B89-4E5C-96E1-DBEE32490567</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,13 +2836,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/103079904</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B21" t="n">
         <v>106813</v>
@@ -2870,10 +2881,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R21" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2911,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2940,13 +2951,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103081007</v>
+        <v>103079906</v>
       </c>
       <c r="B22" t="n">
         <v>106813</v>
@@ -2985,10 +2996,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619923</v>
+        <v>619707</v>
       </c>
       <c r="R22" t="n">
-        <v>6353374</v>
+        <v>6353508</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,17 +3026,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>3F570828-1095-4017-888D-5AEA0E87528E</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,7 +3056,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3055,13 +3066,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081007</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103081008</v>
+        <v>103081007</v>
       </c>
       <c r="B23" t="n">
         <v>106813</v>
@@ -3100,10 +3111,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619861</v>
+        <v>619923</v>
       </c>
       <c r="R23" t="n">
-        <v>6353346</v>
+        <v>6353374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3141,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>D396CCA3-F902-4282-A08D-B86E9D98F9EC</t>
+          <t>3F570828-1095-4017-888D-5AEA0E87528E</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3170,13 +3181,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081008</t>
+          <t>https://artportalen.se/Sighting/103081007</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103081009</v>
+        <v>103081008</v>
       </c>
       <c r="B24" t="n">
         <v>106813</v>
@@ -3215,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619864</v>
+        <v>619861</v>
       </c>
       <c r="R24" t="n">
-        <v>6353395</v>
+        <v>6353346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3245,7 +3256,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>880AB878-6FF7-4C8D-A7D4-792D75F42128</t>
+          <t>D396CCA3-F902-4282-A08D-B86E9D98F9EC</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3256,11 +3267,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>sitter ihop vid basen med andra träd</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3290,13 +3296,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081009</t>
+          <t>https://artportalen.se/Sighting/103081008</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103081010</v>
+        <v>103081009</v>
       </c>
       <c r="B25" t="n">
         <v>106813</v>
@@ -3335,10 +3341,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619799</v>
+        <v>619864</v>
       </c>
       <c r="R25" t="n">
-        <v>6353394</v>
+        <v>6353395</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,17 +3371,22 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>EA10AFF1-FA6B-4DBF-ABE7-0ED882187D3A</t>
+          <t>880AB878-6FF7-4C8D-A7D4-792D75F42128</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sitter ihop vid basen med andra träd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,13 +3416,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081010</t>
+          <t>https://artportalen.se/Sighting/103081009</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103081012</v>
+        <v>103081010</v>
       </c>
       <c r="B26" t="n">
         <v>106813</v>
@@ -3450,10 +3461,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619828</v>
+        <v>619799</v>
       </c>
       <c r="R26" t="n">
-        <v>6353455</v>
+        <v>6353394</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,7 +3491,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>6D610089-8D90-4E4B-A125-EF74BA73A94F</t>
+          <t>EA10AFF1-FA6B-4DBF-ABE7-0ED882187D3A</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3520,13 +3531,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081012</t>
+          <t>https://artportalen.se/Sighting/103081010</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103081013</v>
+        <v>103081012</v>
       </c>
       <c r="B27" t="n">
         <v>106813</v>
@@ -3565,10 +3576,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619836</v>
+        <v>619828</v>
       </c>
       <c r="R27" t="n">
-        <v>6353463</v>
+        <v>6353455</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3595,7 +3606,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>AE0D7AFF-D01F-43D9-86F3-24C6E661F27E</t>
+          <t>6D610089-8D90-4E4B-A125-EF74BA73A94F</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3635,13 +3646,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081013</t>
+          <t>https://artportalen.se/Sighting/103081012</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103081015</v>
+        <v>103081013</v>
       </c>
       <c r="B28" t="n">
         <v>106813</v>
@@ -3680,10 +3691,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619920</v>
+        <v>619836</v>
       </c>
       <c r="R28" t="n">
-        <v>6353549</v>
+        <v>6353463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,7 +3721,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B79E88BA-D07A-43F4-8572-3D235E52B086</t>
+          <t>AE0D7AFF-D01F-43D9-86F3-24C6E661F27E</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3750,13 +3761,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081015</t>
+          <t>https://artportalen.se/Sighting/103081013</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103081016</v>
+        <v>103081015</v>
       </c>
       <c r="B29" t="n">
         <v>106813</v>
@@ -3795,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619738</v>
+        <v>619920</v>
       </c>
       <c r="R29" t="n">
-        <v>6353522</v>
+        <v>6353549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3825,17 +3836,17 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>B79E88BA-D07A-43F4-8572-3D235E52B086</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3865,13 +3876,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103081015</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103092125</v>
+        <v>103081016</v>
       </c>
       <c r="B30" t="n">
         <v>106813</v>
@@ -3904,20 +3915,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619698</v>
+        <v>619738</v>
       </c>
       <c r="R30" t="n">
-        <v>6353451</v>
+        <v>6353522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3944,7 +3951,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3D1CB81E-7170-4C45-914C-8109B2AC73AB</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3963,7 +3970,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3975,7 +3981,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3985,13 +3991,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103092125</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103092126</v>
+        <v>103092125</v>
       </c>
       <c r="B31" t="n">
         <v>106813</v>
@@ -4034,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619717</v>
+        <v>619698</v>
       </c>
       <c r="R31" t="n">
-        <v>6353349</v>
+        <v>6353451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,7 +4070,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FB6CBE85-05C6-44E6-81E2-6634D28C07A1</t>
+          <t>3D1CB81E-7170-4C45-914C-8109B2AC73AB</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4105,13 +4111,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103092126</t>
+          <t>https://artportalen.se/Sighting/103092125</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103178427</v>
+        <v>103092126</v>
       </c>
       <c r="B32" t="n">
         <v>106813</v>
@@ -4144,16 +4150,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619878</v>
+        <v>619717</v>
       </c>
       <c r="R32" t="n">
-        <v>6353474</v>
+        <v>6353349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4180,17 +4190,17 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>300FC56E-18DA-47E9-B79E-E83D2DD6B969</t>
+          <t>FB6CBE85-05C6-44E6-81E2-6634D28C07A1</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4199,6 +4209,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4220,13 +4231,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178427</t>
+          <t>https://artportalen.se/Sighting/103092126</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103178428</v>
+        <v>103178427</v>
       </c>
       <c r="B33" t="n">
         <v>106813</v>
@@ -4265,10 +4276,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619913</v>
+        <v>619878</v>
       </c>
       <c r="R33" t="n">
-        <v>6353429</v>
+        <v>6353474</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4295,7 +4306,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0E6B57D3-C6EC-4BE2-87D0-E0F8724A1584</t>
+          <t>300FC56E-18DA-47E9-B79E-E83D2DD6B969</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4335,13 +4346,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178428</t>
+          <t>https://artportalen.se/Sighting/103178427</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103178429</v>
+        <v>103178428</v>
       </c>
       <c r="B34" t="n">
         <v>106813</v>
@@ -4380,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619912</v>
+        <v>619913</v>
       </c>
       <c r="R34" t="n">
-        <v>6353385</v>
+        <v>6353429</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4410,7 +4421,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>65966497-EB6B-414C-B6BD-0A806D87FC26</t>
+          <t>0E6B57D3-C6EC-4BE2-87D0-E0F8724A1584</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4450,13 +4461,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178429</t>
+          <t>https://artportalen.se/Sighting/103178428</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103178430</v>
+        <v>103178429</v>
       </c>
       <c r="B35" t="n">
         <v>106813</v>
@@ -4495,10 +4506,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619872</v>
+        <v>619912</v>
       </c>
       <c r="R35" t="n">
-        <v>6353320</v>
+        <v>6353385</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4525,7 +4536,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>90AAC376-573C-4DAC-B167-05D3FB3B57C6</t>
+          <t>65966497-EB6B-414C-B6BD-0A806D87FC26</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4565,13 +4576,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178430</t>
+          <t>https://artportalen.se/Sighting/103178429</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103178431</v>
+        <v>103178430</v>
       </c>
       <c r="B36" t="n">
         <v>106813</v>
@@ -4610,10 +4621,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619892</v>
+        <v>619872</v>
       </c>
       <c r="R36" t="n">
-        <v>6353334</v>
+        <v>6353320</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4640,7 +4651,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>EEDB4CED-058C-4E60-BFA5-33CB82CE63C8</t>
+          <t>90AAC376-573C-4DAC-B167-05D3FB3B57C6</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4680,13 +4691,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178431</t>
+          <t>https://artportalen.se/Sighting/103178430</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103178432</v>
+        <v>103178431</v>
       </c>
       <c r="B37" t="n">
         <v>106813</v>
@@ -4725,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619883</v>
+        <v>619892</v>
       </c>
       <c r="R37" t="n">
-        <v>6353353</v>
+        <v>6353334</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4755,7 +4766,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>CCA3107A-9777-47E5-85CA-351B612793FE</t>
+          <t>EEDB4CED-058C-4E60-BFA5-33CB82CE63C8</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4795,13 +4806,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178432</t>
+          <t>https://artportalen.se/Sighting/103178431</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103178433</v>
+        <v>103178432</v>
       </c>
       <c r="B38" t="n">
         <v>106813</v>
@@ -4840,10 +4851,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619849</v>
+        <v>619883</v>
       </c>
       <c r="R38" t="n">
-        <v>6353336</v>
+        <v>6353353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4870,7 +4881,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>7D669A2B-F07F-4D33-BDE7-750519D0DDF6</t>
+          <t>CCA3107A-9777-47E5-85CA-351B612793FE</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4910,13 +4921,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178433</t>
+          <t>https://artportalen.se/Sighting/103178432</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103178434</v>
+        <v>103178433</v>
       </c>
       <c r="B39" t="n">
         <v>106813</v>
@@ -4955,10 +4966,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619868</v>
+        <v>619849</v>
       </c>
       <c r="R39" t="n">
-        <v>6353372</v>
+        <v>6353336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4985,7 +4996,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>9AD321F0-99BB-4C53-BEBF-D9F93C709529</t>
+          <t>7D669A2B-F07F-4D33-BDE7-750519D0DDF6</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5025,13 +5036,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178434</t>
+          <t>https://artportalen.se/Sighting/103178433</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103178435</v>
+        <v>103178434</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5070,10 +5081,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619867</v>
+        <v>619868</v>
       </c>
       <c r="R40" t="n">
-        <v>6353366</v>
+        <v>6353372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5100,7 +5111,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>62728D91-AA41-43C8-A828-4C78D4DD0020</t>
+          <t>9AD321F0-99BB-4C53-BEBF-D9F93C709529</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5140,13 +5151,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178435</t>
+          <t>https://artportalen.se/Sighting/103178434</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103178436</v>
+        <v>103178435</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5185,10 +5196,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619826</v>
+        <v>619867</v>
       </c>
       <c r="R41" t="n">
-        <v>6353457</v>
+        <v>6353366</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5215,17 +5226,17 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C9EB6754-CBE2-41AE-8FAF-190A9B89838E</t>
+          <t>62728D91-AA41-43C8-A828-4C78D4DD0020</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5255,13 +5266,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178436</t>
+          <t>https://artportalen.se/Sighting/103178435</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103178437</v>
+        <v>103178436</v>
       </c>
       <c r="B42" t="n">
         <v>106813</v>
@@ -5300,10 +5311,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619828</v>
+        <v>619826</v>
       </c>
       <c r="R42" t="n">
-        <v>6353474</v>
+        <v>6353457</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5330,7 +5341,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>EA320C07-BE96-48B7-BAAE-044276D753A8</t>
+          <t>C9EB6754-CBE2-41AE-8FAF-190A9B89838E</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5370,13 +5381,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178437</t>
+          <t>https://artportalen.se/Sighting/103178436</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103178438</v>
+        <v>103178437</v>
       </c>
       <c r="B43" t="n">
         <v>106813</v>
@@ -5415,10 +5426,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619718</v>
+        <v>619828</v>
       </c>
       <c r="R43" t="n">
-        <v>6353383</v>
+        <v>6353474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,17 +5456,17 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B65015C3-3308-4FBB-B5C3-D0CC59FDB966</t>
+          <t>EA320C07-BE96-48B7-BAAE-044276D753A8</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5485,13 +5496,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178438</t>
+          <t>https://artportalen.se/Sighting/103178437</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103178439</v>
+        <v>103178438</v>
       </c>
       <c r="B44" t="n">
         <v>106813</v>
@@ -5530,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619700</v>
+        <v>619718</v>
       </c>
       <c r="R44" t="n">
-        <v>6353388</v>
+        <v>6353383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5560,7 +5571,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>9C66160C-F248-4255-B3E9-4C274E84F7E8</t>
+          <t>B65015C3-3308-4FBB-B5C3-D0CC59FDB966</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5600,13 +5611,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178439</t>
+          <t>https://artportalen.se/Sighting/103178438</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103178440</v>
+        <v>103178439</v>
       </c>
       <c r="B45" t="n">
         <v>106813</v>
@@ -5645,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619684</v>
+        <v>619700</v>
       </c>
       <c r="R45" t="n">
-        <v>6353427</v>
+        <v>6353388</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5675,7 +5686,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B8B26C92-CD55-48C0-8CD6-CE8C8B76D4FA</t>
+          <t>9C66160C-F248-4255-B3E9-4C274E84F7E8</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5715,13 +5726,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178440</t>
+          <t>https://artportalen.se/Sighting/103178439</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103178441</v>
+        <v>103178440</v>
       </c>
       <c r="B46" t="n">
         <v>106813</v>
@@ -5760,10 +5771,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619658</v>
+        <v>619684</v>
       </c>
       <c r="R46" t="n">
-        <v>6353411</v>
+        <v>6353427</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5790,7 +5801,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>588AE9B3-D43D-4D56-8712-C6B8D076A3AC</t>
+          <t>B8B26C92-CD55-48C0-8CD6-CE8C8B76D4FA</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5830,13 +5841,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178441</t>
+          <t>https://artportalen.se/Sighting/103178440</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103178442</v>
+        <v>103178441</v>
       </c>
       <c r="B47" t="n">
         <v>106813</v>
@@ -5875,10 +5886,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619673</v>
+        <v>619658</v>
       </c>
       <c r="R47" t="n">
-        <v>6353431</v>
+        <v>6353411</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5905,7 +5916,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>47F4DBEA-F8BB-4709-BFFB-105A7830225F</t>
+          <t>588AE9B3-D43D-4D56-8712-C6B8D076A3AC</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5945,13 +5956,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178442</t>
+          <t>https://artportalen.se/Sighting/103178441</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103178444</v>
+        <v>103178442</v>
       </c>
       <c r="B48" t="n">
         <v>106813</v>
@@ -5990,10 +6001,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619676</v>
+        <v>619673</v>
       </c>
       <c r="R48" t="n">
-        <v>6353448</v>
+        <v>6353431</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6020,7 +6031,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>47F4DBEA-F8BB-4709-BFFB-105A7830225F</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6060,13 +6071,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103178442</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B49" t="n">
         <v>106813</v>
@@ -6105,10 +6116,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R49" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6135,7 +6146,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6175,13 +6186,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B50" t="n">
         <v>106813</v>
@@ -6220,10 +6231,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R50" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6250,7 +6261,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6290,33 +6301,33 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6792798</v>
+        <v>103178446</v>
       </c>
       <c r="B51" t="n">
-        <v>103682</v>
+        <v>106813</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222002</v>
+        <v>220785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6324,20 +6335,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Enerums stugby syd, Öl</t>
+          <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619700</v>
+        <v>619706</v>
       </c>
       <c r="R51" t="n">
-        <v>6353357</v>
+        <v>6353481</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6359,14 +6374,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6381,31 +6401,31 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6792798</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>61074517</v>
+        <v>6792798</v>
       </c>
       <c r="B52" t="n">
-        <v>104254</v>
+        <v>103682</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6413,16 +6433,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222056</v>
+        <v>222002</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6430,24 +6450,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Enerum, stugbyn i SV, Öl</t>
+          <t>Enerums stugby syd, Öl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619837</v>
+        <v>619700</v>
       </c>
       <c r="R52" t="n">
-        <v>6353537</v>
+        <v>6353357</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6471,17 +6487,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2016-08-18</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2016-08-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Kring Enerums träsgate 95</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6492,21 +6503,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Stig i al, ask, hassel</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Wendt</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Wendt, Vera Wendt</t>
+          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6516,13 +6522,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61074517</t>
+          <t>https://artportalen.se/Sighting/6792798</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>61074518</v>
+        <v>61074517</v>
       </c>
       <c r="B53" t="n">
         <v>104254</v>
@@ -6561,10 +6567,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619827</v>
+        <v>619837</v>
       </c>
       <c r="R53" t="n">
-        <v>6353517</v>
+        <v>6353537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6601,7 +6607,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt vid stigar o körvägar</t>
+          <t>Kring Enerums träsgate 95</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6615,7 +6621,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Al, ask, hassel, något fuktigt</t>
+          <t>Stig i al, ask, hassel</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6636,13 +6642,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61074518</t>
+          <t>https://artportalen.se/Sighting/61074517</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>61074519</v>
+        <v>61074518</v>
       </c>
       <c r="B54" t="n">
         <v>104254</v>
@@ -6681,10 +6687,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619792</v>
+        <v>619827</v>
       </c>
       <c r="R54" t="n">
-        <v>6353537</v>
+        <v>6353517</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6721,7 +6727,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Kring Enerums träsgate 95</t>
+          <t>Rikligt vid stigar o körvägar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6735,7 +6741,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Stigar längs 50 m</t>
+          <t>Al, ask, hassel, något fuktigt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6756,13 +6762,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61074519</t>
+          <t>https://artportalen.se/Sighting/61074518</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>61074520</v>
+        <v>61074519</v>
       </c>
       <c r="B55" t="n">
         <v>104254</v>
@@ -6792,25 +6798,22 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Enerum, stugbyn i SV, Öl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619747</v>
+        <v>619792</v>
       </c>
       <c r="R55" t="n">
-        <v>6353531</v>
+        <v>6353537</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6844,7 +6847,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Enerums träsgate i sydväst</t>
+          <t>Kring Enerums träsgate 95</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6858,7 +6861,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Vägren längs 10 m i al, ask, hassel</t>
+          <t>Stigar längs 50 m</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6878,6 +6881,129 @@
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61074519</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>61074520</v>
+      </c>
+      <c r="B56" t="n">
+        <v>104254</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Enerum, stugbyn i SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>619747</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6353531</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2016-08-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2016-08-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Enerums träsgate i sydväst</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Vägren längs 10 m i al, ask, hassel</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Göran Wendt, Vera Wendt</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/61074520</t>
         </is>
@@ -6939,6 +7065,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2741-2022 artfynd.xlsx
+++ b/artfynd/S 2741-2022 artfynd.xlsx
@@ -1573,7 +1573,7 @@
         <v>136643875</v>
       </c>
       <c r="B10" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
